--- a/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
+++ b/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\share\OneDrive\Documents\Personal Projects\GOGO Kart\CAD\GOGO_KART_FSAE\Suspension\3D_Suspension_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07802B9-1BE1-4F32-AE95-11B5107DEA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8B354D-890D-4EFB-8E7E-6B750D6F6125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
+    <workbookView xWindow="-23136" yWindow="4164" windowWidth="23232" windowHeight="12432" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="186">
   <si>
     <t>Value</t>
   </si>
@@ -555,6 +555,48 @@
   </si>
   <si>
     <t>z component of the vector from TI to point F</t>
+  </si>
+  <si>
+    <t>Front Upper</t>
+  </si>
+  <si>
+    <t>Front Lower</t>
+  </si>
+  <si>
+    <t>Rear Upper</t>
+  </si>
+  <si>
+    <t>Rear Lower</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Member Length (mm)</t>
+  </si>
+  <si>
+    <t>Camber - KPI Offset</t>
+  </si>
+  <si>
+    <t>Suspension Configuration (Input Values into Suspension Hardpoints)</t>
+  </si>
+  <si>
+    <t>Front Pivot  Horizontal Position  (Approximate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Pivot Longitudinal Position </t>
+  </si>
+  <si>
+    <t>Rear Pivot Horizontal Position  (Approximate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rear Pivot Vertical Position </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rear Pivot Longitudinal Position </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Pivot Vertical Position </t>
   </si>
 </sst>
 </file>
@@ -574,7 +616,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,6 +668,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,7 +748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -753,6 +807,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -879,7 +944,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>8940752</xdr:colOff>
+      <xdr:colOff>8950277</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>40170</xdr:rowOff>
     </xdr:to>
@@ -971,9 +1036,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>5474073</xdr:colOff>
+      <xdr:colOff>5481693</xdr:colOff>
       <xdr:row>108</xdr:row>
-      <xdr:rowOff>98312</xdr:rowOff>
+      <xdr:rowOff>109742</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1434,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523DEDE4-CF63-4BE7-9597-216ED5BF300E}">
-  <dimension ref="C3:K55"/>
+  <dimension ref="C3:Q55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
@@ -1447,23 +1512,23 @@
     <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="114.7109375" customWidth="1"/>
     <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="22.85546875" customWidth="1"/>
-    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
-    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
+    <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C3" s="14" t="s">
         <v>86</v>
       </c>
@@ -1476,8 +1541,15 @@
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M3" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+    </row>
+    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1502,8 +1574,23 @@
       <c r="K4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1528,8 +1615,23 @@
       <c r="K5" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M5" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="N5" s="23">
+        <v>370</v>
+      </c>
+      <c r="O5" s="23">
+        <v>380</v>
+      </c>
+      <c r="P5" s="23">
+        <v>390</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1554,8 +1656,23 @@
       <c r="K6" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M6" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="N6" s="25">
+        <v>289</v>
+      </c>
+      <c r="O6" s="25">
+        <v>274</v>
+      </c>
+      <c r="P6" s="25">
+        <v>289</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1580,8 +1697,23 @@
       <c r="K7" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M7" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="N7" s="25">
+        <v>350</v>
+      </c>
+      <c r="O7" s="25">
+        <v>350</v>
+      </c>
+      <c r="P7" s="25">
+        <v>350</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1606,8 +1738,23 @@
       <c r="K8" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M8" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="N8" s="25">
+        <v>360</v>
+      </c>
+      <c r="O8" s="25">
+        <v>350</v>
+      </c>
+      <c r="P8" s="25">
+        <v>2180</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1632,8 +1779,23 @@
       <c r="K9" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M9" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="N9" s="25">
+        <v>289</v>
+      </c>
+      <c r="O9" s="25">
+        <v>274</v>
+      </c>
+      <c r="P9" s="25">
+        <v>289</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1658,8 +1820,23 @@
       <c r="K10" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M10" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="N10" s="25">
+        <v>350</v>
+      </c>
+      <c r="O10" s="25">
+        <v>350</v>
+      </c>
+      <c r="P10" s="25">
+        <v>350</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
@@ -1684,8 +1861,23 @@
       <c r="K11" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M11" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="N11" s="25">
+        <v>620</v>
+      </c>
+      <c r="O11" s="25">
+        <v>610</v>
+      </c>
+      <c r="P11" s="25">
+        <v>2440</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>14</v>
       </c>
@@ -1711,7 +1903,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="4" t="s">
         <v>16</v>
       </c>
@@ -1724,8 +1916,15 @@
       <c r="F13" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M13" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
         <v>15</v>
       </c>
@@ -1744,8 +1943,15 @@
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M14" s="26">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+    </row>
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1771,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
@@ -2683,7 +2889,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M14:Q14"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C38:F38"/>

--- a/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
+++ b/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\share\OneDrive\Documents\Personal Projects\GOGO Kart\CAD\GOGO_KART_FSAE\Suspension\3D_Suspension_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8B354D-890D-4EFB-8E7E-6B750D6F6125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ABEC80-4971-4A07-B670-1DB9582C9F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="4164" windowWidth="23232" windowHeight="12432" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="2" r:id="rId1"/>
@@ -785,6 +785,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -807,17 +818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1529,25 +1529,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="H3" s="14" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="H3" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="M3" s="22" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="M3" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
     </row>
     <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
@@ -1618,16 +1618,16 @@
       <c r="M5" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="14">
         <v>370</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="14">
         <v>380</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="14">
         <v>390</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="14">
         <v>400</v>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="4">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>18</v>
@@ -1656,19 +1656,19 @@
       <c r="K6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="16">
         <v>289</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="16">
         <v>274</v>
       </c>
-      <c r="P6" s="25">
+      <c r="P6" s="16">
         <v>289</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="Q6" s="16">
         <v>274</v>
       </c>
     </row>
@@ -1697,19 +1697,19 @@
       <c r="K7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="16">
         <v>350</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="16">
         <v>350</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="16">
         <v>350</v>
       </c>
-      <c r="Q7" s="25">
+      <c r="Q7" s="16">
         <v>350</v>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>18</v>
@@ -1738,19 +1738,19 @@
       <c r="K8" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="16">
         <v>360</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="16">
         <v>350</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="16">
         <v>2180</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="16">
         <v>2180</v>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="4">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>18</v>
@@ -1779,19 +1779,19 @@
       <c r="K9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="16">
         <v>289</v>
       </c>
-      <c r="O9" s="25">
+      <c r="O9" s="16">
         <v>274</v>
       </c>
-      <c r="P9" s="25">
+      <c r="P9" s="16">
         <v>289</v>
       </c>
-      <c r="Q9" s="25">
+      <c r="Q9" s="16">
         <v>274</v>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="4">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>18</v>
@@ -1820,19 +1820,19 @@
       <c r="K10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="16">
         <v>350</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O10" s="16">
         <v>350</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P10" s="16">
         <v>350</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q10" s="16">
         <v>350</v>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="4">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>18</v>
@@ -1861,19 +1861,19 @@
       <c r="K11" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="16">
         <v>620</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="16">
         <v>610</v>
       </c>
-      <c r="P11" s="25">
+      <c r="P11" s="16">
         <v>2440</v>
       </c>
-      <c r="Q11" s="25">
+      <c r="Q11" s="16">
         <v>2440</v>
       </c>
     </row>
@@ -1916,13 +1916,13 @@
       <c r="F13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
@@ -1937,19 +1937,19 @@
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17"/>
-      <c r="M14" s="26">
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="M14" s="18">
         <v>0</v>
       </c>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
     </row>
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I17" s="7">
         <f>D5+D22*COS(RADIANS(I16))</f>
-        <v>209.54451150103324</v>
+        <v>446.41016151377545</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>18</v>
@@ -2019,18 +2019,18 @@
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
       <c r="H18" s="5" t="s">
         <v>129</v>
       </c>
       <c r="I18" s="7">
         <f>D6+D22*SIN(RADIANS(I16))</f>
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>18</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="I19" s="7">
         <f>SQRT((I17-D7)^2 + (I18-D8)^2)</f>
-        <v>147.24734449232466</v>
+        <v>395.92474848202028</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>18</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="I20" s="8">
         <f>DEGREES(ATAN((I18-D8)/(I17-D7)))</f>
-        <v>28.384783475547717</v>
+        <v>22.263078447401128</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>1</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I21" s="5">
         <f>DEGREES(ACOS((D23^2 + I19^2 - D27^2)/(2*D23*I19)))</f>
-        <v>65.710463226864007</v>
+        <v>33.324157300390048</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>1</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D22" s="9">
         <f>SQRT((D9)^2-(D20/2)^2)</f>
-        <v>109.54451150103323</v>
+        <v>346.41016151377545</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>18</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I22" s="8">
         <f>I20+(I12*I21)</f>
-        <v>-37.325679751316287</v>
+        <v>-11.061078852988921</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>1</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D23" s="9">
         <f>SQRT((D10)^2-(D21/2)^2)</f>
-        <v>124.49899597988733</v>
+        <v>357.07142142714252</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>18</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I23" s="5">
         <f>D7+(D23)*(COS(RADIANS(I22)))</f>
-        <v>179.00182560944995</v>
+        <v>430.43818353042815</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>18</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="I24" s="5">
         <f>D8+(D23)*(SIN(RADIANS(I22)))</f>
-        <v>-45.48932723237148</v>
+        <v>131.49394534864837</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>18</v>
@@ -2235,12 +2235,12 @@
       <c r="F26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="21"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="26"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="3" t="s">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D27" s="9">
         <f>SQRT((D11^2)-(D26^2))</f>
-        <v>148.66068747318505</v>
+        <v>219.08902300206645</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>18</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D28" s="9">
         <f>D5+D22*COS(RADIANS(D16))</f>
-        <v>209.54451150103324</v>
+        <v>446.41016151377545</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>18</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D29" s="9">
         <f>D6+D22*SIN(RADIANS(D16))</f>
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>18</v>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I29" s="3">
         <f>I23+I9</f>
-        <v>169.00182560944995</v>
+        <v>420.43818353042815</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>18</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D30" s="9">
         <f>SQRT((D28-D7)^2 + (D29-D8)^2)</f>
-        <v>147.24734449232466</v>
+        <v>395.92474848202028</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>18</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" s="3">
         <f>I24+I10</f>
-        <v>-35.48932723237148</v>
+        <v>141.49394534864837</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>18</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D31" s="9">
         <f>DEGREES(ATAN(((D29-D8)/(D28-D7))))</f>
-        <v>28.384783475547717</v>
+        <v>22.263078447401128</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>1</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I31" s="3">
         <f>SQRT((I28-I5)^2+(I29-I6)^2+(I30-I7)^2)</f>
-        <v>110.49966942558504</v>
+        <v>358.23045188105499</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>18</v>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D32" s="9">
         <f>DEGREES(ACOS((D23^2 + D30^2 - D27^2)/(2*D23*D30)))</f>
-        <v>65.710463226864007</v>
+        <v>33.324157300390048</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I33" s="11">
         <f>D26/D11</f>
-        <v>0.13333333333333333</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>18</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D34" s="9">
         <f>D31+(D33*D32)</f>
-        <v>-37.325679751316287</v>
+        <v>-11.061078852988921</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>1</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I34" s="11">
         <f>(D28-D35)/D11</f>
-        <v>0.20361790594388859</v>
+        <v>7.2599899924305919E-2</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>18</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D35" s="9">
         <f>D7+(D23)*(COS(RADIANS(D34)))</f>
-        <v>179.00182560944995</v>
+        <v>430.43818353042815</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>18</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="I35" s="11">
         <f>(D29-D36)/D11</f>
-        <v>0.96992884821580982</v>
+        <v>0.99320933932432565</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>18</v>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D36" s="9">
         <f>D8+(D23)*(SIN(RADIANS(D34)))</f>
-        <v>-45.48932723237148</v>
+        <v>131.49394534864837</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>18</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="I36" s="4">
         <f>-DEGREES(ATAN((I17-I23)/(I18-I24)))</f>
-        <v>-11.855979792562804</v>
+        <v>-4.1806725892062859</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>1</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I37" s="11">
         <f>D41</f>
-        <v>-11.855979792562804</v>
+        <v>-4.1806725892062859</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>1</v>
@@ -2536,12 +2536,12 @@
       </c>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
       <c r="H38" s="4" t="s">
         <v>96</v>
       </c>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D40" s="10">
         <f>DEGREES(ATAN(D26/(D29-D36)))</f>
-        <v>7.8272280346744827</v>
+        <v>5.2297474141121247</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>1</v>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D41" s="10">
         <f>-DEGREES(ATAN((D28-D35)/(D29-D36)))</f>
-        <v>-11.855979792562804</v>
+        <v>-4.1806725892062859</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>1</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D42" s="10">
         <f>(D28-D5)*(D36-D8)-(D29-D6)*(D35-D7)</f>
-        <v>-8269.4414752117791</v>
+        <v>-23731.193456446246</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>76</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="I42" s="9">
         <f>I39*I33+I40*I34+I41*I35</f>
-        <v>6.3297760893858781</v>
+        <v>8.297003484909288</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>18</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D43" s="10">
         <f>D5 + (((D7-D5)*(D36-D8)-(D8-D6)*(D35-D7))/D42)*(D28-D5)</f>
-        <v>-11.802749431441569</v>
+        <v>-687.3150613779668</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>18</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I43" s="12">
         <f>I39-I42*I33</f>
-        <v>-10.843970145251451</v>
+        <v>-10.754273044082662</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>18</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D44" s="6">
         <f>D6 + (((D7-D5)*(D36-D8)-(D8-D6)*(D35-D7))/D42)*(D29-D6)</f>
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>18</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I44" s="12">
         <f>I40-I42*I34</f>
-        <v>-11.288855752414449</v>
+        <v>-10.602361622676032</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>18</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I45" s="12">
         <f>I41-I42*I35</f>
-        <v>3.8605675681579825</v>
+        <v>1.7593386503816184</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>18</v>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="I46" s="3">
         <f>SQRT(I43^2+I44^2+I45^2)</f>
-        <v>16.122466767161868</v>
+        <v>15.203938081017141</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>18</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="I47" s="12">
         <f>I34*I41-I35*I40</f>
-        <v>11.735467541596984</v>
+        <v>10.658092392486315</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>18</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="I48" s="12">
         <f>I35*I39-I33*I41</f>
-        <v>-11.032621815491432</v>
+        <v>-10.841184302334167</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>18</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I49" s="12">
         <f>I33*I40-I34*I39</f>
-        <v>0.70284572610555274</v>
+        <v>-0.18309190984784995</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>18</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I50" s="13">
         <f>D25+I42*I33</f>
-        <v>160.84397014525146</v>
+        <v>160.75427304408265</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>18</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I51" s="13">
         <f>D35+I42*I34</f>
-        <v>180.29068136186439</v>
+        <v>431.04054515310418</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>18</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I52" s="13">
         <f>D36+I42*I35</f>
-        <v>-39.349894800529462</v>
+        <v>139.73460669826676</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>18</v>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I53" s="13">
         <f>I50-I5</f>
-        <v>10.843970145251461</v>
+        <v>10.754273044082652</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>18</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I54" s="13">
         <f>I51-I6</f>
-        <v>100.29068136186439</v>
+        <v>351.04054515310418</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>18</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="I55" s="13">
         <f>I52-I7</f>
-        <v>-69.349894800529455</v>
+        <v>109.73460669826676</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>18</v>
@@ -2890,15 +2890,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H26:K26"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="M13:Q13"/>
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H26:K26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
+++ b/Suspension/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\share\OneDrive\Documents\Personal Projects\GOGO Kart\CAD\GOGO_KART_FSAE\Suspension\3D_Suspension_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29ABEC80-4971-4A07-B670-1DB9582C9F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059059EE-CE1E-422D-8A54-239D7D1CA805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="206">
   <si>
     <t>Value</t>
   </si>
@@ -597,6 +597,66 @@
   </si>
   <si>
     <t xml:space="preserve">Front Pivot Vertical Position </t>
+  </si>
+  <si>
+    <t>Calculated Final Steering Values (Tie Rod Spin Equation)</t>
+  </si>
+  <si>
+    <t>A_coeff</t>
+  </si>
+  <si>
+    <t>Weight of the cos term in the spin equation (A cos + B sin = C) 2x the dot product of g (the vector from the tie-rod anchor TI to the circle center L) with R⊥ (the rest-radius LM).</t>
+  </si>
+  <si>
+    <t>B_coeff</t>
+  </si>
+  <si>
+    <t>The weight on the sine term. Twice the dot product of g with w (the full-length partner radius, 90° around the circle in the n_hat x R direction).</t>
+  </si>
+  <si>
+    <t>C_coeff</t>
+  </si>
+  <si>
+    <t>R_amp</t>
+  </si>
+  <si>
+    <t>The amplitude of the single combined wave. Adding a cosine wave weighted by A to a sine wave weighted by B always gives one wave, this is its height.</t>
+  </si>
+  <si>
+    <t>The fixed target the cosine-and-sine combination must equal.</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>phi</t>
+  </si>
+  <si>
+    <t>head_x</t>
+  </si>
+  <si>
+    <t>head_y</t>
+  </si>
+  <si>
+    <t>TOE ANGLE</t>
+  </si>
+  <si>
+    <t>The phase shift of the combined wave</t>
+  </si>
+  <si>
+    <t>The spin angle (the amount the rest-radius LM must rotate about the axis n to become the actual radius LN)</t>
+  </si>
+  <si>
+    <t>The fore/aft component of the wheel's forward-pointing arrow after it's been spun by φ about the axis n̂.</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>The lateral component of that same spun forward arrow</t>
+  </si>
+  <si>
+    <t>The wheel's steer angle</t>
   </si>
 </sst>
 </file>
@@ -616,7 +676,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,6 +740,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -790,6 +856,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1030,15 +1102,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>708772</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>140073</xdr:rowOff>
+      <xdr:colOff>372596</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>84043</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>5481693</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>109742</xdr:rowOff>
+      <xdr:colOff>4865370</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>53712</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1061,8 +1133,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15915154" y="11760573"/>
-          <a:ext cx="6905625" cy="8911739"/>
+          <a:off x="15601390" y="13609543"/>
+          <a:ext cx="6913245" cy="8923169"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1499,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523DEDE4-CF63-4BE7-9597-216ED5BF300E}">
-  <dimension ref="C3:Q55"/>
+  <dimension ref="C3:Q67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
@@ -1508,9 +1580,9 @@
     <col min="6" max="6" width="159" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="114.7109375" customWidth="1"/>
+    <col min="11" max="11" width="153.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.42578125" customWidth="1"/>
     <col min="13" max="13" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -1529,25 +1601,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="H3" s="19" t="s">
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="H3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="M3" s="17" t="s">
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="M3" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
@@ -1916,13 +1988,13 @@
       <c r="F13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="4" t="s">
@@ -1937,19 +2009,19 @@
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="M14" s="18">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="24"/>
+      <c r="M14" s="20">
         <v>0</v>
       </c>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
     </row>
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="4" t="s">
@@ -2019,12 +2091,12 @@
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24"/>
       <c r="H18" s="5" t="s">
         <v>129</v>
       </c>
@@ -2140,7 +2212,7 @@
         <v>131</v>
       </c>
       <c r="I22" s="8">
-        <f>I20+(I12*I21)</f>
+        <f>I20+(D33*I21)</f>
         <v>-11.061078852988921</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -2235,12 +2307,12 @@
       <c r="F26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="28"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="3" t="s">
@@ -2536,12 +2608,12 @@
       </c>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
       <c r="H38" s="4" t="s">
         <v>96</v>
       </c>
@@ -2888,8 +2960,166 @@
         <v>171</v>
       </c>
     </row>
+    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H57" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+    </row>
+    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H59" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="I59" s="18">
+        <f>2*(I53*I43+I54*I44+I55*I45)</f>
+        <v>-7288.9057155850824</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H60" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="I60" s="18">
+        <f>2*(I53*I47+I54*I48+I55*I49)</f>
+        <v>-7422.3334611911832</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H61" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I61" s="17">
+        <f>I31^2-(I53^2+I54^2+I55^2)-I46^2</f>
+        <v>-7288.9057155851069</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H62" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I62" s="17">
+        <f>SQRT(I59^2+I60^2)</f>
+        <v>10402.844829170874</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H63" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="I63" s="17">
+        <f>DEGREES(ATAN2(I59,I60))</f>
+        <v>-134.48035396695602</v>
+      </c>
+      <c r="J63" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H64" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="I64" s="17">
+        <f>I63+I12*DEGREES(ACOS(I61/I62))</f>
+        <v>-268.9607079339122</v>
+      </c>
+      <c r="J64" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H65" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="I65" s="17">
+        <f>COS(RADIANS(I64))+I33^2*(1-COS(RADIANS(I64)))</f>
+        <v>-9.7237095099381669E-3</v>
+      </c>
+      <c r="J65" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="66" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H66" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="I66" s="17">
+        <f>I35*SIN(RADIANS(I64))+I33*I34*(1-COS(RADIANS(I64)))</f>
+        <v>0.99976565007767926</v>
+      </c>
+      <c r="J66" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H67" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="I67" s="17">
+        <f>I11+DEGREES(ATAN2(I65,I66))</f>
+        <v>90.557240539272001</v>
+      </c>
+      <c r="J67" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="H57:K57"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="H14:K14"/>
